--- a/tools/importer/reports/import-faq.report.xlsx
+++ b/tools/importer/reports/import-faq.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="122">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,7 +58,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:23.894Z</t>
+    <t>2026-09-28T08:40:28.985Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -67,12 +67,33 @@
     <t>https://wknd.site/us/en.html</t>
   </si>
   <si>
+    <t>us/en/about-us.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>["cards","cards","cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>us/en/about-us</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>2026-09-28T06:49:29.123Z</t>
+  </si>
+  <si>
+    <t>About Us</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/about-us.html</t>
+  </si>
+  <si>
     <t>us/en/adventures.report.json</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>["hero-teaser","cards-article"]</t>
   </si>
   <si>
@@ -82,7 +103,7 @@
     <t>adventure-listing</t>
   </si>
   <si>
-    <t>2026-09-28T06:21:34.372Z</t>
+    <t>2026-09-28T08:42:00.642Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -103,7 +124,7 @@
     <t>faq</t>
   </si>
   <si>
-    <t>2026-09-28T06:37:54.159Z</t>
+    <t>2026-09-28T08:42:07.878Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -124,7 +145,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:30.781Z</t>
+    <t>2026-09-28T08:40:37.145Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -133,22 +154,37 @@
     <t>https://wknd.site/us/en/magazine.html</t>
   </si>
   <si>
+    <t>us/en/adventures/bali-surf-camp.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-hero","cards-related","tabs"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/bali-surf-camp</t>
+  </si>
+  <si>
+    <t>adventure</t>
+  </si>
+  <si>
+    <t>2026-09-28T08:41:52.456Z</t>
+  </si>
+  <si>
+    <t>Bali Surf Camp</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/bali-surf-camp.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/climbing-new-zealand.report.json</t>
   </si>
   <si>
     <t>["What to Bring — empty alt, used tab label"]</t>
   </si>
   <si>
-    <t>["carousel-hero","cards-related","tabs"]</t>
-  </si>
-  <si>
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>adventure</t>
-  </si>
-  <si>
-    <t>2026-09-28T06:11:14.621Z</t>
+    <t>2026-09-28T08:41:15.257Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -157,13 +193,28 @@
     <t>https://wknd.site/us/en/adventures/climbing-new-zealand.html</t>
   </si>
   <si>
+    <t>us/en/adventures/cycling-southern-utah.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-southern-utah</t>
+  </si>
+  <si>
+    <t>2026-09-28T08:41:46.894Z</t>
+  </si>
+  <si>
+    <t>Cycling Southern Utah</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/cycling-southern-utah.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/downhill-skiing-wyoming.report.json</t>
   </si>
   <si>
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-28T06:11:19.916Z</t>
+    <t>2026-09-28T08:41:20.412Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -178,7 +229,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-28T06:11:26.660Z</t>
+    <t>2026-09-28T08:41:25.316Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -193,7 +244,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-28T06:11:32.880Z</t>
+    <t>2026-09-28T08:41:30.818Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -211,7 +262,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-28T06:11:37.918Z</t>
+    <t>2026-09-28T08:41:36.824Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -226,7 +277,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-28T06:11:42.534Z</t>
+    <t>2026-09-28T08:41:41.885Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -250,7 +301,7 @@
     <t>article</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:42.238Z</t>
+    <t>2026-09-28T08:40:49.424Z</t>
   </si>
   <si>
     <t>Arctic Surfing</t>
@@ -268,7 +319,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:48.423Z</t>
+    <t>2026-09-28T08:40:56.213Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -283,7 +334,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:52.683Z</t>
+    <t>2026-09-28T08:41:01.781Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -301,7 +352,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:56.697Z</t>
+    <t>2026-09-28T08:41:06.680Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -319,7 +370,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-09-28T05:59:37.701Z</t>
+    <t>2026-09-28T08:40:44.775Z</t>
   </si>
   <si>
     <t>Western Australia</t>
@@ -714,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -875,39 +926,39 @@
         <v>40</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>44</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>45</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>46</v>
-      </c>
-      <c r="I6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
         <v>49</v>
@@ -916,239 +967,239 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
         <v>76</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
         <v>77</v>
       </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>78</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>79</v>
-      </c>
-      <c r="H12" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
         <v>82</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
         <v>83</v>
       </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="H13" t="s">
         <v>84</v>
       </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>85</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" t="s">
         <v>89</v>
       </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>90</v>
-      </c>
-      <c r="H14" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
         <v>93</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>94</v>
       </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
         <v>95</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>78</v>
       </c>
       <c r="G15" t="s">
         <v>96</v>
@@ -1168,7 +1219,7 @@
         <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -1177,7 +1228,7 @@
         <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s">
         <v>102</v>
@@ -1187,6 +1238,93 @@
       </c>
       <c r="I16" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-faq.report.xlsx
+++ b/tools/importer/reports/import-faq.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="167">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,7 +58,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-28T08:40:28.985Z</t>
+    <t>2026-09-28T10:08:08.824Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -82,7 +82,7 @@
     <t>about</t>
   </si>
   <si>
-    <t>2026-09-28T06:49:29.123Z</t>
+    <t>2026-09-28T08:42:15.364Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -103,7 +103,7 @@
     <t>adventure-listing</t>
   </si>
   <si>
-    <t>2026-09-28T08:42:00.642Z</t>
+    <t>2026-09-28T10:10:11.179Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -124,7 +124,7 @@
     <t>faq</t>
   </si>
   <si>
-    <t>2026-09-28T08:42:07.878Z</t>
+    <t>2026-09-28T10:10:18.317Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -145,7 +145,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-09-28T08:40:37.145Z</t>
+    <t>2026-09-28T10:08:16.325Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -166,7 +166,7 @@
     <t>adventure</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:52.456Z</t>
+    <t>2026-09-28T10:09:23.862Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -175,6 +175,24 @@
     <t>https://wknd.site/us/en/adventures/bali-surf-camp.html</t>
   </si>
   <si>
+    <t>us/en/adventures/beervana-portland.report.json</t>
+  </si>
+  <si>
+    <t>["Overview — empty alt, used tab label"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/beervana-portland</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:29.409Z</t>
+  </si>
+  <si>
+    <t>Beervana in Portland</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/beervana-portland.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/climbing-new-zealand.report.json</t>
   </si>
   <si>
@@ -184,7 +202,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:15.257Z</t>
+    <t>2026-09-28T10:08:49.829Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -193,13 +211,28 @@
     <t>https://wknd.site/us/en/adventures/climbing-new-zealand.html</t>
   </si>
   <si>
+    <t>us/en/adventures/colorado-rock-climbing.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/colorado-rock-climbing</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:33.753Z</t>
+  </si>
+  <si>
+    <t>Colorado Rock Climbing</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/colorado-rock-climbing.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/cycling-southern-utah.report.json</t>
   </si>
   <si>
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:46.894Z</t>
+    <t>2026-09-28T10:09:18.776Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -208,13 +241,31 @@
     <t>https://wknd.site/us/en/adventures/cycling-southern-utah.html</t>
   </si>
   <si>
+    <t>us/en/adventures/cycling-tuscany.report.json</t>
+  </si>
+  <si>
+    <t>["Action shot of cyclists riding hard. (image 2) — duplicate alt"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/cycling-tuscany</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:39.183Z</t>
+  </si>
+  <si>
+    <t>Cycling Tuscany</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/cycling-tuscany.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/downhill-skiing-wyoming.report.json</t>
   </si>
   <si>
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:20.412Z</t>
+    <t>2026-09-28T10:08:55.386Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -223,13 +274,97 @@
     <t>https://wknd.site/us/en/adventures/downhill-skiing-wyoming.html</t>
   </si>
   <si>
+    <t>us/en/adventures/gastronomic-marais-tour.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/gastronomic-marais-tour</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:43.387Z</t>
+  </si>
+  <si>
+    <t>Gastronomic Marais Tour</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/gastronomic-marais-tour.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/napa-wine-tasting.report.json</t>
+  </si>
+  <si>
+    <t>us/en/adventures/napa-wine-tasting</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:48.226Z</t>
+  </si>
+  <si>
+    <t>Napa Wine Tasting</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/napa-wine-tasting.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/riverside-camping-australia.report.json</t>
+  </si>
+  <si>
+    <t>["Adobe waadobe wa mg — empty alt, used file name","What to Bring — empty alt, used tab label"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/riverside-camping-australia</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:53.233Z</t>
+  </si>
+  <si>
+    <t>Riverside Camping</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/riverside-camping-australia.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/ski-touring-mont-blanc.report.json</t>
+  </si>
+  <si>
+    <t>["Alpiniste sur l'ascension du Mont-Blanc (4810m) au niveau du dôme du Goûter, Alpiniste sur l'ascension du Mont-Blanc… (image 2) — duplicate alt","Itinerary — empty alt, used tab label"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/ski-touring-mont-blanc</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:09:59.187Z</t>
+  </si>
+  <si>
+    <t>Ski Touring Mont Blanc</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/ski-touring-mont-blanc.html</t>
+  </si>
+  <si>
+    <t>us/en/adventures/surf-camp-costa-rica.report.json</t>
+  </si>
+  <si>
+    <t>["Overview — empty alt, used tab label","Itinerary — empty alt, used tab label"]</t>
+  </si>
+  <si>
+    <t>us/en/adventures/surf-camp-costa-rica</t>
+  </si>
+  <si>
+    <t>2026-09-28T10:10:03.937Z</t>
+  </si>
+  <si>
+    <t>Surf Camp in Costa Rica</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/adventures/surf-camp-costa-rica.html</t>
+  </si>
+  <si>
     <t>us/en/adventures/tahoe-skiing.report.json</t>
   </si>
   <si>
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:25.316Z</t>
+    <t>2026-09-28T10:09:00.277Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -244,7 +379,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:30.818Z</t>
+    <t>2026-09-28T10:09:05.423Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -262,7 +397,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:36.824Z</t>
+    <t>2026-09-28T10:09:09.328Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -277,7 +412,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:41.885Z</t>
+    <t>2026-09-28T10:09:15.033Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -301,7 +436,7 @@
     <t>article</t>
   </si>
   <si>
-    <t>2026-09-28T08:40:49.424Z</t>
+    <t>2026-09-28T10:08:28.284Z</t>
   </si>
   <si>
     <t>Arctic Surfing</t>
@@ -319,7 +454,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-09-28T08:40:56.213Z</t>
+    <t>2026-09-28T10:08:33.111Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -334,7 +469,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:01.781Z</t>
+    <t>2026-09-28T10:08:37.651Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -352,7 +487,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-09-28T08:41:06.680Z</t>
+    <t>2026-09-28T10:08:43.381Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -370,7 +505,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-09-28T08:40:44.775Z</t>
+    <t>2026-09-28T10:08:23.128Z</t>
   </si>
   <si>
     <t>Western Australia</t>
@@ -765,11 +900,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="8" width="33" customWidth="1"/>
@@ -1013,13 +1148,13 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -1028,18 +1163,18 @@
         <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -1048,7 +1183,7 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1057,18 +1192,18 @@
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1077,7 +1212,7 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1086,27 +1221,27 @@
         <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -1115,27 +1250,27 @@
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -1144,18 +1279,18 @@
         <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -1164,7 +1299,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -1173,158 +1308,390 @@
         <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
         <v>93</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
         <v>94</v>
       </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>95</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>96</v>
-      </c>
-      <c r="H15" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
         <v>99</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
         <v>100</v>
       </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="H16" t="s">
         <v>101</v>
       </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>102</v>
-      </c>
-      <c r="H16" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
         <v>105</v>
       </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" t="s">
         <v>106</v>
       </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>107</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>108</v>
-      </c>
-      <c r="I17" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
         <v>110</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
         <v>111</v>
       </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
         <v>112</v>
       </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>113</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>114</v>
-      </c>
-      <c r="I18" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
         <v>116</v>
       </c>
-      <c r="B19" t="s">
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" t="s">
         <v>117</v>
       </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="H19" t="s">
         <v>118</v>
       </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>119</v>
       </c>
-      <c r="H19" t="s">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>120</v>
       </c>
-      <c r="I19" t="s">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
         <v>121</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" t="s">
+        <v>123</v>
+      </c>
+      <c r="I20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" t="s">
+        <v>164</v>
+      </c>
+      <c r="H27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I27" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
